--- a/output/graficos_regionales_cobertura/plot_comunal_cobertura_2024_arica_y_parinacota.xlsx
+++ b/output/graficos_regionales_cobertura/plot_comunal_cobertura_2024_arica_y_parinacota.xlsx
@@ -51,7 +51,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-08 13:53</t>
+    <t xml:space="preserve">2026-09-09 20:17</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_regionales_cobertura/plot_comunal_cobertura_2024_arica_y_parinacota.xlsx
+++ b/output/graficos_regionales_cobertura/plot_comunal_cobertura_2024_arica_y_parinacota.xlsx
@@ -51,7 +51,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 20:17</t>
+    <t xml:space="preserve">2026-09-18 17:07</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_regionales_cobertura/plot_comunal_cobertura_2024_arica_y_parinacota.xlsx
+++ b/output/graficos_regionales_cobertura/plot_comunal_cobertura_2024_arica_y_parinacota.xlsx
@@ -30,18 +30,18 @@
     <t xml:space="preserve">Cobertura</t>
   </si>
   <si>
+    <t xml:space="preserve">Arica</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Putre</t>
+  </si>
+  <si>
+    <t xml:space="preserve">General Lagos</t>
+  </si>
+  <si>
     <t xml:space="preserve">Camarones</t>
   </si>
   <si>
-    <t xml:space="preserve">General Lagos</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Putre</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Arica</t>
-  </si>
-  <si>
     <t xml:space="preserve">Campo</t>
   </si>
   <si>
@@ -51,7 +51,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 17:07</t>
+    <t xml:space="preserve">2026-09-27 21:55</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -471,13 +471,13 @@
         <v>4</v>
       </c>
       <c r="B2" s="2" t="n">
-        <v>585</v>
+        <v>252826</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>1246</v>
+        <v>257163</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>46.95</v>
+        <v>98.31</v>
       </c>
     </row>
     <row r="3">
@@ -485,13 +485,13 @@
         <v>5</v>
       </c>
       <c r="B3" s="2" t="n">
-        <v>381</v>
+        <v>1327</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>801</v>
+        <v>2569</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>47.57</v>
+        <v>51.65</v>
       </c>
     </row>
     <row r="4">
@@ -499,13 +499,13 @@
         <v>6</v>
       </c>
       <c r="B4" s="2" t="n">
-        <v>1327</v>
+        <v>381</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>2569</v>
+        <v>801</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>51.65</v>
+        <v>47.57</v>
       </c>
     </row>
     <row r="5">
@@ -513,13 +513,13 @@
         <v>7</v>
       </c>
       <c r="B5" s="2" t="n">
-        <v>252826</v>
+        <v>585</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>257163</v>
+        <v>1246</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>98.31</v>
+        <v>46.95</v>
       </c>
     </row>
   </sheetData>

--- a/output/graficos_regionales_cobertura/plot_comunal_cobertura_2024_arica_y_parinacota.xlsx
+++ b/output/graficos_regionales_cobertura/plot_comunal_cobertura_2024_arica_y_parinacota.xlsx
@@ -51,7 +51,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-27 21:55</t>
+    <t xml:space="preserve">2026-10-05 05:52</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
